--- a/data/trans_bre/P1408-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1408-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-15,72%</t>
+          <t>-15,53%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,29</t>
+          <t>-3,27; 0,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,05</t>
+          <t>-3,65; 0,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,23</t>
+          <t>-1,31; 1,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,87</t>
+          <t>-2,08; 0,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-70,86; 16,45</t>
+          <t>-71,43; 15,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-78,77; 9,16</t>
+          <t>-76,73; 15,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-64,04; 159,15</t>
+          <t>-66,1; 155,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-50,69; 38,33</t>
+          <t>-48,96; 39,85</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -0,78</t>
+          <t>-4,36; -0,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,08; -0,04</t>
+          <t>-2,12; 0,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,39</t>
+          <t>-1,93; 0,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,25</t>
+          <t>-1,01; 1,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,68; -17,56</t>
+          <t>-70,55; -19,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-78,68; 13,84</t>
+          <t>-78,64; 7,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-69,28; 31,22</t>
+          <t>-68,97; 37,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 176,57</t>
+          <t>-34,73; 86,1</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>-0,34</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-36,33%</t>
+          <t>-15,1%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,37</t>
+          <t>-2,41; 1,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,28</t>
+          <t>-2,31; 0,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,4</t>
+          <t>-1,33; 1,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 0,55</t>
+          <t>-1,72; 1,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-52,91; 55,68</t>
+          <t>-52,16; 61,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-82,69; 37,26</t>
+          <t>-80,65; 40,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-62,28; 151,22</t>
+          <t>-56,72; 134,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,89; 30,61</t>
+          <t>-56,31; 76,27</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,4</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 0,5</t>
+          <t>-2,77; 0,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,64</t>
+          <t>-1,34; 0,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,93; -0,56</t>
+          <t>-2,79; -0,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,61</t>
+          <t>-0,91; 1,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,62; 16,95</t>
+          <t>-55,66; 12,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,63; 70,37</t>
+          <t>-63,39; 86,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-87,77; -25,15</t>
+          <t>-88,16; -28,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,16; 80,58</t>
+          <t>-29,2; 74,52</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,31; -0,53</t>
+          <t>-2,3; -0,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; -0,37</t>
+          <t>-1,59; -0,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; -0,05</t>
+          <t>-1,29; -0,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,76</t>
+          <t>-0,67; 0,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-50,09; -14,79</t>
+          <t>-50,59; -16,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-62,11; -18,5</t>
+          <t>-62,96; -15,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-55,12; -2,5</t>
+          <t>-57,23; -1,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-27,73; 37,78</t>
+          <t>-23,1; 32,4</t>
         </is>
       </c>
     </row>
